--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>320000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>520000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>64197.53</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>39506.17</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>64197.53</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,183 +117,225 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>520000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>64197.53</t>
+          <t>700000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>86283.42</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>64197.53</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>86283.42</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,183 +159,225 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>yxhgq52</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>700000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>86283.42</t>
+          <t>1000000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>121997.71</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>86283.42</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>121997.71</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -325,59 +325,86 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>06/24 12:43:13</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1000000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>121997.71</t>
+          <t>1000000</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>121997.71</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>121997.71</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>121409.71</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,210 +201,252 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1000000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>121997.71</t>
+          <t>1320000</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>161503.88</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>121409.71</t>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>160915.88</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,210 +243,252 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1320000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>161503.88</t>
+          <t>1720000</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>210886.6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>160915.88</t>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>210298.6</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,210 +285,252 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1720000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>210886.6</t>
+          <t>2020000</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>247923.63</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>210298.6</t>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>247335.63</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,210 +327,252 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2020000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>247923.63</t>
+          <t>2180000</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>267676.72</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>247335.63</t>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>267088.72</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,210 +369,252 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2180000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>267676.72</t>
+          <t>2280000</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>280022.4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>267088.72</t>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>279434.4</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,210 +411,252 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2280000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>280022.4</t>
+          <t>2580000</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>317289.48</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>279434.4</t>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>316701.48</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,210 +453,252 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2580000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>317289.48</t>
+          <t>2780000</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>342134.2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>316701.48</t>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>341546.2</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,210 +495,252 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2780000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>342134.2</t>
+          <t>3280000</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>404246</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>341546.2</t>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>403658</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,210 +537,252 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3280000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>404246</t>
+          <t>4220000</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>521746</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>403658</t>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>521158</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,210 +579,252 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>4220000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>521746</t>
+          <t>4500000</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>556313.9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>521158</t>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>555725.9</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -748,83 +748,110 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>4500000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>556313.9</t>
+          <t>4500000</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>556313.9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>555725.9</t>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>555675.9</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,237 +621,279 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>4500000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>556313.9</t>
+          <t>4820000</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>596065.45</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>555675.9</t>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>595427.45</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,237 +663,279 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>4820000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>596065.45</t>
+          <t>5100000</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>630633.36</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>595427.45</t>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>629995.36</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,237 +705,279 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>5100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>630633.36</t>
+          <t>5200000</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>642903.29</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>629995.36</t>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>642265.29</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,237 +747,279 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>5200000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>642903.29</t>
+          <t>5350000</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>661421.81</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>642265.29</t>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>660783.81</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -916,12 +916,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -943,83 +943,110 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>5350000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>661421.81</t>
+          <t>5350000</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>661421.81</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>826</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>660783.81</t>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>660595.81</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,166 +789,181 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -970,83 +985,110 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>5350000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>661421.81</t>
+          <t>5630000</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>696421.81</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>826</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>660595.81</t>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>695595.81</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,166 +831,181 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1012,83 +1027,110 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>5630000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>696421.81</t>
+          <t>5730000</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>708616.93</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>826</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>695595.81</t>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>707790.93</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,166 +873,181 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1054,83 +1069,110 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>5730000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>708616.93</t>
+          <t>6120000</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>756765.08</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>826</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>707790.93</t>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>755939.08</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,166 +915,181 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1096,83 +1111,110 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>6120000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>756765.08</t>
+          <t>6370000</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>788015.08</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>826</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>755939.08</t>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>787189.08</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,22 +90,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,166 +957,181 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1138,83 +1153,110 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>6370000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>788015.08</t>
+          <t>6369990</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>788005.08</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>826</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>787189.08</t>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>787179.08</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,22 +90,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,22 +132,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,166 +999,181 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1180,83 +1195,110 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>6369990</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>788005.08</t>
+          <t>6599990</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>816755.08</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>826</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>787179.08</t>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>815929.08</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,22 +132,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,22 +174,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,166 +1041,181 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1222,83 +1237,110 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>6599990</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>816755.08</t>
+          <t>6699990</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>829177.44</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>826</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>815929.08</t>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>828351.44</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,22 +174,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,22 +216,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,166 +1083,181 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1264,83 +1279,110 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>6699990</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>829177.44</t>
+          <t>7764390</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>962227.44</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>826</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>828351.44</t>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>961401.44</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,22 +216,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,22 +258,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,166 +1125,181 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1306,83 +1321,110 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="40"/>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>7764390</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>962227.44</t>
+          <t>8089390</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>1003366.68</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>826</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>961401.44</t>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1002540.68</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,39 +90,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,22 +258,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,22 +300,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,166 +1167,181 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1348,83 +1363,110 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>8089390</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1003366.68</t>
+          <t>8089378</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>1003354.68</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>826</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>1002540.68</t>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1002528.68</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,39 +90,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,39 +132,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,22 +300,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,22 +342,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,166 +1209,181 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1390,83 +1405,110 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="42"/>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>8089378</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1003354.68</t>
+          <t>8189378</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>1015624.62</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>826</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>1002528.68</t>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1014798.62</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,39 +132,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,39 +174,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,22 +342,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,22 +384,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,166 +1251,181 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1432,83 +1447,110 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="43"/>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>8189378</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1015624.62</t>
+          <t>8689378</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>1075865.59</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>826</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>1014798.62</t>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1075039.59</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,39 +174,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,39 +216,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,22 +384,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,22 +426,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,166 +1293,181 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1474,83 +1489,110 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>8689378</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1075865.59</t>
+          <t>8739378</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>1082000.56</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>826</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>1075039.59</t>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1081174.56</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -1462,12 +1462,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1489,12 +1489,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1516,83 +1516,110 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="45"/>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>8739378</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1082000.56</t>
+          <t>8739378</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>1082000.56</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>1081174.56</t>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1080898.56</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,39 +216,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,39 +258,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,22 +426,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,22 +468,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,166 +1335,181 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1516,12 +1531,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1543,83 +1558,110 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="46"/>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="47"/>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>8739378</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1082000.56</t>
+          <t>9039378</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1119267.64</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>1080898.56</t>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1118165.64</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/07 17:03:42</t>
+          <t>07/08 11:27:56</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>23952.1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,39 +258,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,39 +300,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,22 +468,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,22 +510,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,166 +1377,181 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="40"/>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1558,12 +1573,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1585,83 +1600,110 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="47"/>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>9039378</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1119267.64</t>
+          <t>9239378</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1143219.73</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>1118165.64</t>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1142117.73</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/08 11:27:56</t>
+          <t>07/08 11:55:35</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>23952.1</t>
+          <t>124223.6</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/07 17:03:42</t>
+          <t>07/08 11:27:56</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>23952.1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,39 +300,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,39 +342,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,22 +510,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,22 +552,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,166 +1419,181 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1600,12 +1615,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1627,83 +1642,110 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="48"/>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>9239378</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1143219.73</t>
+          <t>10239378</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1267443.33</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>1142117.73</t>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1266341.33</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/08 11:55:35</t>
+          <t>07/09 09:51:15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>124223.6</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/08 11:27:56</t>
+          <t>07/08 11:55:35</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>23952.1</t>
+          <t>124223.6</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/07 17:03:42</t>
+          <t>07/08 11:27:56</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>23952.1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,39 +342,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,39 +384,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,22 +552,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,22 +594,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,166 +1461,181 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="42"/>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1642,12 +1657,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1669,83 +1684,110 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="49"/>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="50"/>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>10239378</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1267443.33</t>
+          <t>10289378</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1273616.17</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>1266341.33</t>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1272514.17</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/09 09:51:15</t>
+          <t>07/09 09:52:18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>45962.73</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/08 11:55:35</t>
+          <t>07/09 09:51:15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>124223.6</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/08 11:27:56</t>
+          <t>07/08 11:55:35</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>23952.1</t>
+          <t>124223.6</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/07 17:03:42</t>
+          <t>07/08 11:27:56</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>23952.1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,39 +384,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,39 +426,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,22 +594,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,22 +636,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1503,166 +1503,181 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="40"/>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="43"/>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1684,12 +1699,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1711,83 +1726,110 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="50"/>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="51"/>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>10289378</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1273616.17</t>
+          <t>10659378</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1319578.91</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>1272514.17</t>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1318476.91</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/09 09:52:18</t>
+          <t>07/09 09:52:57</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>45962.73</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/09 09:51:15</t>
+          <t>07/09 09:52:18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>45962.73</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/08 11:55:35</t>
+          <t>07/09 09:51:15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>124223.6</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/08 11:27:56</t>
+          <t>07/08 11:55:35</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>23952.1</t>
+          <t>124223.6</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/07 17:03:42</t>
+          <t>07/08 11:27:56</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>23952.1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,39 +426,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,39 +468,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,22 +636,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,22 +678,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,12 +1518,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1545,166 +1545,181 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1726,12 +1741,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1753,83 +1768,110 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="51"/>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>10659378</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1319578.91</t>
+          <t>10759378</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1331627.1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>1318476.91</t>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1330525.1</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/09 09:52:57</t>
+          <t>07/09 20:44:16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/09 09:52:18</t>
+          <t>07/09 09:52:57</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>45962.73</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/09 09:51:15</t>
+          <t>07/09 09:52:18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>45962.73</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/08 11:55:35</t>
+          <t>07/09 09:51:15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>124223.6</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/08 11:27:56</t>
+          <t>07/08 11:55:35</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>23952.1</t>
+          <t>124223.6</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/07 17:03:42</t>
+          <t>07/08 11:27:56</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>23952.1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,39 +468,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,39 +510,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,22 +678,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,22 +720,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,12 +1518,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1587,166 +1587,181 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="42"/>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="45"/>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1768,12 +1783,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1795,83 +1810,110 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="52"/>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="53"/>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>10759378</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1331627.1</t>
+          <t>10859378</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1343675.29</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>1330525.1</t>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1342573.29</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/09 20:44:16</t>
+          <t>07/10 13:24:33</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>29543.18</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,7 +117,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/09 09:52:57</t>
+          <t>07/09 20:44:16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/09 09:52:18</t>
+          <t>07/09 09:52:57</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>45962.73</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/09 09:51:15</t>
+          <t>07/09 09:52:18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>45962.73</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/08 11:55:35</t>
+          <t>07/09 09:51:15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>124223.6</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/08 11:27:56</t>
+          <t>07/08 11:55:35</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>23952.1</t>
+          <t>124223.6</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/07 17:03:42</t>
+          <t>07/08 11:27:56</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>23952.1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,39 +510,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,39 +552,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,22 +720,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,22 +762,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,12 +1518,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1629,166 +1629,181 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="43"/>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="46"/>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="47"/>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1810,12 +1825,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1837,83 +1852,110 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="53"/>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>10859378</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1343675.29</t>
+          <t>11119358</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1373218.47</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>1342573.29</t>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1372116.47</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/10 13:24:33</t>
+          <t>07/10 13:44:44</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>29543.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/09 20:44:16</t>
+          <t>07/10 13:24:33</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>29543.18</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,7 +159,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/09 09:52:57</t>
+          <t>07/09 20:44:16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/09 09:52:18</t>
+          <t>07/09 09:52:57</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>45962.73</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/09 09:51:15</t>
+          <t>07/09 09:52:18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>45962.73</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/08 11:55:35</t>
+          <t>07/09 09:51:15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>124223.6</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/08 11:27:56</t>
+          <t>07/08 11:55:35</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>23952.1</t>
+          <t>124223.6</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/07 17:03:42</t>
+          <t>07/08 11:27:56</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>23952.1</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,39 +552,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,39 +594,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,22 +762,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,22 +804,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1671,166 +1671,181 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="47"/>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1852,12 +1867,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1879,83 +1894,110 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="54"/>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="55"/>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>11119358</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1373218.47</t>
+          <t>11219358</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1385413.6</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>1372116.47</t>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1384311.6</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/10 13:44:44</t>
+          <t>07/10 14:54:56</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>36809.82</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/10 13:24:33</t>
+          <t>07/10 13:44:44</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>29543.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/09 20:44:16</t>
+          <t>07/10 13:24:33</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>29543.18</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,7 +201,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/09 09:52:57</t>
+          <t>07/09 20:44:16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/09 09:52:18</t>
+          <t>07/09 09:52:57</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>45962.73</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/09 09:51:15</t>
+          <t>07/09 09:52:18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>45962.73</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/08 11:55:35</t>
+          <t>07/09 09:51:15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>124223.6</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/08 11:27:56</t>
+          <t>07/08 11:55:35</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>23952.1</t>
+          <t>124223.6</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/07 17:03:42</t>
+          <t>07/08 11:27:56</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>23952.1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,39 +594,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,39 +636,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,22 +804,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,22 +846,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1713,166 +1713,181 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="45"/>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="48"/>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1894,12 +1909,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1921,83 +1936,110 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="55"/>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="56"/>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>11219358</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1385413.6</t>
+          <t>11519358</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1422223.41</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>1384311.6</t>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1421121.41</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/10 14:54:56</t>
+          <t>07/12 14:43:07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>36809.82</t>
+          <t>18404.91</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/10 13:44:44</t>
+          <t>07/10 14:54:56</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>36809.82</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/10 13:24:33</t>
+          <t>07/10 13:44:44</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>29543.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/09 20:44:16</t>
+          <t>07/10 13:24:33</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>29543.18</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,7 +243,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/09 09:52:57</t>
+          <t>07/09 20:44:16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/09 09:52:18</t>
+          <t>07/09 09:52:57</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>45962.73</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/09 09:51:15</t>
+          <t>07/09 09:52:18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>45962.73</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/08 11:55:35</t>
+          <t>07/09 09:51:15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>124223.6</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/08 11:27:56</t>
+          <t>07/08 11:55:35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>23952.1</t>
+          <t>124223.6</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/07 17:03:42</t>
+          <t>07/08 11:27:56</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>23952.1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,39 +636,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,39 +678,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,22 +846,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,22 +888,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1713,12 +1713,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1755,166 +1755,181 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="46"/>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="47"/>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="49"/>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="50"/>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1936,12 +1951,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1963,83 +1978,110 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="56"/>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="57"/>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>11519358</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1422223.41</t>
+          <t>11669358</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1440628.32</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>1421121.41</t>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1439526.32</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/12 14:43:07</t>
+          <t>07/13 10:45:12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>600000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/10 14:54:56</t>
+          <t>07/12 14:43:07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>36809.82</t>
+          <t>18404.91</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/10 13:44:44</t>
+          <t>07/10 14:54:56</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>36809.82</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/10 13:24:33</t>
+          <t>07/10 13:44:44</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>29543.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/09 20:44:16</t>
+          <t>07/10 13:24:33</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>29543.18</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,7 +285,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/09 09:52:57</t>
+          <t>07/09 20:44:16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/09 09:52:18</t>
+          <t>07/09 09:52:57</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>45962.73</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/09 09:51:15</t>
+          <t>07/09 09:52:18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>45962.73</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/08 11:55:35</t>
+          <t>07/09 09:51:15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>124223.6</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/08 11:27:56</t>
+          <t>07/08 11:55:35</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23952.1</t>
+          <t>124223.6</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/07 17:03:42</t>
+          <t>07/08 11:27:56</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>23952.1</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,39 +678,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,39 +720,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,22 +888,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,22 +930,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1713,12 +1713,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1797,166 +1797,181 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="47"/>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="50"/>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="51"/>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1978,12 +1993,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2005,83 +2020,110 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="57"/>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="58"/>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>11669358</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1440628.32</t>
+          <t>12269358</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1515628.32</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>1439526.32</t>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1514526.32</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/13 10:45:12</t>
+          <t>07/13 12:08:35</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>600000</t>
+          <t>175000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>21341.46</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/12 14:43:07</t>
+          <t>07/13 10:45:12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>600000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/10 14:54:56</t>
+          <t>07/12 14:43:07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>36809.82</t>
+          <t>18404.91</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/10 13:44:44</t>
+          <t>07/10 14:54:56</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>36809.82</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/10 13:24:33</t>
+          <t>07/10 13:44:44</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>29543.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/09 20:44:16</t>
+          <t>07/10 13:24:33</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>29543.18</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,7 +327,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/09 09:52:57</t>
+          <t>07/09 20:44:16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/09 09:52:18</t>
+          <t>07/09 09:52:57</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>45962.73</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/09 09:51:15</t>
+          <t>07/09 09:52:18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>45962.73</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/08 11:55:35</t>
+          <t>07/09 09:51:15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>124223.6</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/08 11:27:56</t>
+          <t>07/08 11:55:35</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>23952.1</t>
+          <t>124223.6</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/07 17:03:42</t>
+          <t>07/08 11:27:56</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>23952.1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,39 +720,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,39 +762,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,22 +930,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,22 +972,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,12 +1518,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1713,12 +1713,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1797,12 +1797,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1839,166 +1839,181 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="48"/>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="51"/>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2020,12 +2035,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2047,83 +2062,110 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="58"/>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="59"/>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>12269358</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1515628.32</t>
+          <t>12444358</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1536969.78</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>1514526.32</t>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1535867.78</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/13 12:08:35</t>
+          <t>07/13 13:36:47</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21341.46</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/13 10:45:12</t>
+          <t>07/13 12:08:35</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>600000</t>
+          <t>175000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>21341.46</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/12 14:43:07</t>
+          <t>07/13 10:45:12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>600000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/10 14:54:56</t>
+          <t>07/12 14:43:07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>36809.82</t>
+          <t>18404.91</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/10 13:44:44</t>
+          <t>07/10 14:54:56</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>36809.82</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/10 13:24:33</t>
+          <t>07/10 13:44:44</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>29543.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/09 20:44:16</t>
+          <t>07/10 13:24:33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>29543.18</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,7 +369,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/09 09:52:57</t>
+          <t>07/09 20:44:16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/09 09:52:18</t>
+          <t>07/09 09:52:57</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>45962.73</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/09 09:51:15</t>
+          <t>07/09 09:52:18</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>45962.73</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/08 11:55:35</t>
+          <t>07/09 09:51:15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>124223.6</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/08 11:27:56</t>
+          <t>07/08 11:55:35</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>23952.1</t>
+          <t>124223.6</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/07 17:03:42</t>
+          <t>07/08 11:27:56</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>23952.1</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,39 +762,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,39 +804,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,22 +972,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,22 +1014,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1713,12 +1713,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1797,12 +1797,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1881,166 +1881,181 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="49"/>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="50"/>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="52"/>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="53"/>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2062,12 +2077,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2089,83 +2104,110 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="59"/>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="60"/>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>12444358</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1536969.78</t>
+          <t>12944358</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1599469.78</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>1535867.78</t>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1598367.78</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/13 13:36:47</t>
+          <t>07/14 19:36:11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>28395.06</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/13 12:08:35</t>
+          <t>07/13 13:36:47</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21341.46</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/13 10:45:12</t>
+          <t>07/13 12:08:35</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>600000</t>
+          <t>175000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>21341.46</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/12 14:43:07</t>
+          <t>07/13 10:45:12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>600000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/10 14:54:56</t>
+          <t>07/12 14:43:07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>36809.82</t>
+          <t>18404.91</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/10 13:44:44</t>
+          <t>07/10 14:54:56</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>36809.82</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/10 13:24:33</t>
+          <t>07/10 13:44:44</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>29543.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/09 20:44:16</t>
+          <t>07/10 13:24:33</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>29543.18</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,7 +411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/09 09:52:57</t>
+          <t>07/09 20:44:16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/09 09:52:18</t>
+          <t>07/09 09:52:57</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>45962.73</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/09 09:51:15</t>
+          <t>07/09 09:52:18</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>45962.73</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/08 11:55:35</t>
+          <t>07/09 09:51:15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>124223.6</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/08 11:27:56</t>
+          <t>07/08 11:55:35</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>23952.1</t>
+          <t>124223.6</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/07 17:03:42</t>
+          <t>07/08 11:27:56</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>23952.1</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,39 +804,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,39 +846,39 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,22 +1014,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,22 +1056,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1713,12 +1713,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1797,12 +1797,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1881,12 +1881,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1923,166 +1923,181 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="50"/>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="51"/>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="53"/>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2104,12 +2119,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2131,83 +2146,110 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="60"/>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="61"/>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>12944358</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1599469.78</t>
+          <t>13174358</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1627864.84</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>1598367.78</t>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1626762.84</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/14 19:36:11</t>
+          <t>07/15 16:22:26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>28395.06</t>
+          <t>13496.93</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/13 13:36:47</t>
+          <t>07/14 19:36:11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>28395.06</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/13 12:08:35</t>
+          <t>07/13 13:36:47</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>21341.46</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/13 10:45:12</t>
+          <t>07/13 12:08:35</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>600000</t>
+          <t>175000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>21341.46</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/12 14:43:07</t>
+          <t>07/13 10:45:12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>600000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/10 14:54:56</t>
+          <t>07/12 14:43:07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>36809.82</t>
+          <t>18404.91</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/10 13:44:44</t>
+          <t>07/10 14:54:56</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>36809.82</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/10 13:24:33</t>
+          <t>07/10 13:44:44</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>29543.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/09 20:44:16</t>
+          <t>07/10 13:24:33</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>29543.18</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/09 09:52:57</t>
+          <t>07/09 20:44:16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/09 09:52:18</t>
+          <t>07/09 09:52:57</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>45962.73</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/09 09:51:15</t>
+          <t>07/09 09:52:18</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>45962.73</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/08 11:55:35</t>
+          <t>07/09 09:51:15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>124223.6</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/08 11:27:56</t>
+          <t>07/08 11:55:35</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>23952.1</t>
+          <t>124223.6</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/07 17:03:42</t>
+          <t>07/08 11:27:56</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>23952.1</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,39 +846,39 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,39 +888,39 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,22 +1056,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,22 +1098,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,12 +1518,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1713,12 +1713,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1797,12 +1797,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1881,12 +1881,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1965,166 +1965,181 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="51"/>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="54"/>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="55"/>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2146,12 +2161,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2173,83 +2188,110 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="61"/>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="62"/>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>13174358</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1627864.84</t>
+          <t>13284358</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1641361.78</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>1626762.84</t>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1640259.78</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/15 16:22:26</t>
+          <t>07/15 19:20:32</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>13496.93</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/14 19:36:11</t>
+          <t>07/15 16:22:26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>28395.06</t>
+          <t>13496.93</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/13 13:36:47</t>
+          <t>07/14 19:36:11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>28395.06</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/13 12:08:35</t>
+          <t>07/13 13:36:47</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>21341.46</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/13 10:45:12</t>
+          <t>07/13 12:08:35</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>600000</t>
+          <t>175000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>21341.46</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/12 14:43:07</t>
+          <t>07/13 10:45:12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>600000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/10 14:54:56</t>
+          <t>07/12 14:43:07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>36809.82</t>
+          <t>18404.91</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/10 13:44:44</t>
+          <t>07/10 14:54:56</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>36809.82</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/10 13:24:33</t>
+          <t>07/10 13:44:44</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>29543.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/09 20:44:16</t>
+          <t>07/10 13:24:33</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>29543.18</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,7 +495,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/09 09:52:57</t>
+          <t>07/09 20:44:16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/09 09:52:18</t>
+          <t>07/09 09:52:57</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>45962.73</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/09 09:51:15</t>
+          <t>07/09 09:52:18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>45962.73</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/08 11:55:35</t>
+          <t>07/09 09:51:15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>124223.6</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/08 11:27:56</t>
+          <t>07/08 11:55:35</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>23952.1</t>
+          <t>124223.6</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/07 17:03:42</t>
+          <t>07/08 11:27:56</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>23952.1</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,39 +888,39 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,39 +930,39 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,22 +1098,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,12 +1518,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1713,12 +1713,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1797,12 +1797,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1881,12 +1881,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1965,12 +1965,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2007,166 +2007,181 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="52"/>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="53"/>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="55"/>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="56"/>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2188,12 +2203,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2215,83 +2230,110 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="62"/>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="63"/>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>13284358</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1641361.78</t>
+          <t>13784358</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1703861.78</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>1640259.78</t>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1702759.78</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/15 19:20:32</t>
+          <t>07/16 12:19:58</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/15 16:22:26</t>
+          <t>07/15 19:20:32</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>13496.93</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/14 19:36:11</t>
+          <t>07/15 16:22:26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>28395.06</t>
+          <t>13496.93</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/13 13:36:47</t>
+          <t>07/14 19:36:11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>28395.06</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/13 12:08:35</t>
+          <t>07/13 13:36:47</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>21341.46</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/13 10:45:12</t>
+          <t>07/13 12:08:35</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>600000</t>
+          <t>175000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>21341.46</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/12 14:43:07</t>
+          <t>07/13 10:45:12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>600000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/10 14:54:56</t>
+          <t>07/12 14:43:07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>36809.82</t>
+          <t>18404.91</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/10 13:44:44</t>
+          <t>07/10 14:54:56</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>36809.82</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/10 13:24:33</t>
+          <t>07/10 13:44:44</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>29543.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/09 20:44:16</t>
+          <t>07/10 13:24:33</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>29543.18</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,7 +537,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/09 09:52:57</t>
+          <t>07/09 20:44:16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/09 09:52:18</t>
+          <t>07/09 09:52:57</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>45962.73</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/09 09:51:15</t>
+          <t>07/09 09:52:18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>45962.73</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/08 11:55:35</t>
+          <t>07/09 09:51:15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>124223.6</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/08 11:27:56</t>
+          <t>07/08 11:55:35</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>23952.1</t>
+          <t>124223.6</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/07 17:03:42</t>
+          <t>07/08 11:27:56</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>23952.1</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,39 +930,39 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,39 +972,39 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,22 +1182,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,12 +1518,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1713,12 +1713,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1797,12 +1797,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1881,12 +1881,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1965,12 +1965,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2049,166 +2049,181 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="53"/>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="56"/>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="57"/>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2230,12 +2245,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2257,83 +2272,110 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="63"/>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>13784358</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1703861.78</t>
+          <t>14004358</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1730052.25</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>1702759.78</t>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>1728950.25</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/16 12:19:58</t>
+          <t>07/17 10:45:36</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>13671.07</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/15 19:20:32</t>
+          <t>07/16 12:19:58</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/15 16:22:26</t>
+          <t>07/15 19:20:32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13496.93</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/14 19:36:11</t>
+          <t>07/15 16:22:26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>28395.06</t>
+          <t>13496.93</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/13 13:36:47</t>
+          <t>07/14 19:36:11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>28395.06</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/13 12:08:35</t>
+          <t>07/13 13:36:47</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>21341.46</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/13 10:45:12</t>
+          <t>07/13 12:08:35</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>600000</t>
+          <t>175000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>21341.46</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/12 14:43:07</t>
+          <t>07/13 10:45:12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>600000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/10 14:54:56</t>
+          <t>07/12 14:43:07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>36809.82</t>
+          <t>18404.91</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/10 13:44:44</t>
+          <t>07/10 14:54:56</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>36809.82</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/10 13:24:33</t>
+          <t>07/10 13:44:44</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>29543.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/09 20:44:16</t>
+          <t>07/10 13:24:33</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>29543.18</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/09 09:52:57</t>
+          <t>07/09 20:44:16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/09 09:52:18</t>
+          <t>07/09 09:52:57</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>45962.73</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/09 09:51:15</t>
+          <t>07/09 09:52:18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>45962.73</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/08 11:55:35</t>
+          <t>07/09 09:51:15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>124223.6</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/08 11:27:56</t>
+          <t>07/08 11:55:35</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>23952.1</t>
+          <t>124223.6</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/07 17:03:42</t>
+          <t>07/08 11:27:56</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>23952.1</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,39 +972,39 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,39 +1014,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,22 +1182,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,22 +1224,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,12 +1518,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1713,12 +1713,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1797,12 +1797,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1881,12 +1881,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1965,12 +1965,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2049,12 +2049,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2091,166 +2091,181 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="54"/>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="55"/>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="57"/>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="58"/>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2272,12 +2287,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2299,83 +2314,110 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="64"/>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="65"/>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>14004358</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1730052.25</t>
+          <t>14125347</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1743723.33</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>1728950.25</t>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1742621.33</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/17 10:45:36</t>
+          <t>07/17 15:25:18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>13671.07</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/16 12:19:58</t>
+          <t>07/17 10:45:36</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>13671.07</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/15 19:20:32</t>
+          <t>07/16 12:19:58</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/15 16:22:26</t>
+          <t>07/15 19:20:32</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13496.93</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/14 19:36:11</t>
+          <t>07/15 16:22:26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>28395.06</t>
+          <t>13496.93</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/13 13:36:47</t>
+          <t>07/14 19:36:11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>28395.06</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/13 12:08:35</t>
+          <t>07/13 13:36:47</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>21341.46</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/13 10:45:12</t>
+          <t>07/13 12:08:35</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>600000</t>
+          <t>175000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>21341.46</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/12 14:43:07</t>
+          <t>07/13 10:45:12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>600000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/10 14:54:56</t>
+          <t>07/12 14:43:07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>36809.82</t>
+          <t>18404.91</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/10 13:44:44</t>
+          <t>07/10 14:54:56</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>36809.82</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/10 13:24:33</t>
+          <t>07/10 13:44:44</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>29543.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/09 20:44:16</t>
+          <t>07/10 13:24:33</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>29543.18</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,7 +621,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/09 09:52:57</t>
+          <t>07/09 20:44:16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/09 09:52:18</t>
+          <t>07/09 09:52:57</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>45962.73</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/09 09:51:15</t>
+          <t>07/09 09:52:18</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>45962.73</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/08 11:55:35</t>
+          <t>07/09 09:51:15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>124223.6</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/08 11:27:56</t>
+          <t>07/08 11:55:35</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>23952.1</t>
+          <t>124223.6</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/07 17:03:42</t>
+          <t>07/08 11:27:56</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>23952.1</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,39 +1014,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,39 +1056,39 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,22 +1224,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,12 +1518,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1713,12 +1713,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1797,12 +1797,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1881,12 +1881,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1965,12 +1965,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2049,12 +2049,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2091,12 +2091,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2106,12 +2106,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2133,166 +2133,181 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="55"/>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="56"/>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="58"/>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="59"/>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2314,12 +2329,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2341,83 +2356,110 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="65"/>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="66"/>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>14125347</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1743723.33</t>
+          <t>14225347</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1755993.27</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>1742621.33</t>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1754891.27</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/17 15:25:18</t>
+          <t>07/17 17:10:27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/17 10:45:36</t>
+          <t>07/17 15:25:18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>13671.07</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/16 12:19:58</t>
+          <t>07/17 10:45:36</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>13671.07</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/15 19:20:32</t>
+          <t>07/16 12:19:58</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/15 16:22:26</t>
+          <t>07/15 19:20:32</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>13496.93</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/14 19:36:11</t>
+          <t>07/15 16:22:26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>28395.06</t>
+          <t>13496.93</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/13 13:36:47</t>
+          <t>07/14 19:36:11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>28395.06</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/13 12:08:35</t>
+          <t>07/13 13:36:47</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>21341.46</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/13 10:45:12</t>
+          <t>07/13 12:08:35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>600000</t>
+          <t>175000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>21341.46</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/12 14:43:07</t>
+          <t>07/13 10:45:12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>600000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/10 14:54:56</t>
+          <t>07/12 14:43:07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>36809.82</t>
+          <t>18404.91</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/10 13:44:44</t>
+          <t>07/10 14:54:56</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>36809.82</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/10 13:24:33</t>
+          <t>07/10 13:44:44</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>29543.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/09 20:44:16</t>
+          <t>07/10 13:24:33</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>29543.18</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,7 +663,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/09 09:52:57</t>
+          <t>07/09 20:44:16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/09 09:52:18</t>
+          <t>07/09 09:52:57</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>45962.73</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/09 09:51:15</t>
+          <t>07/09 09:52:18</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>45962.73</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/08 11:55:35</t>
+          <t>07/09 09:51:15</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>124223.6</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/08 11:27:56</t>
+          <t>07/08 11:55:35</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>23952.1</t>
+          <t>124223.6</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/07 17:03:42</t>
+          <t>07/08 11:27:56</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>23952.1</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,39 +1056,39 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,39 +1098,39 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,22 +1308,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,12 +1518,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1713,12 +1713,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1797,12 +1797,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1881,12 +1881,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1965,12 +1965,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2049,12 +2049,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2091,12 +2091,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2106,12 +2106,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2133,12 +2133,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2175,166 +2175,181 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="56"/>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="57"/>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="59"/>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="60"/>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2356,12 +2371,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2383,83 +2398,110 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="66"/>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="67"/>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>14225347</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1755993.27</t>
+          <t>14475347</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1787243.27</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>1754891.27</t>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>1786141.27</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/17 17:10:27</t>
+          <t>07/17 18:14:47</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>183843</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>22557.42</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/17 15:25:18</t>
+          <t>07/17 17:10:27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/17 10:45:36</t>
+          <t>07/17 15:25:18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13671.07</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/16 12:19:58</t>
+          <t>07/17 10:45:36</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>13671.07</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/15 19:20:32</t>
+          <t>07/16 12:19:58</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/15 16:22:26</t>
+          <t>07/15 19:20:32</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>13496.93</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/14 19:36:11</t>
+          <t>07/15 16:22:26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>28395.06</t>
+          <t>13496.93</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/13 13:36:47</t>
+          <t>07/14 19:36:11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>28395.06</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/13 12:08:35</t>
+          <t>07/13 13:36:47</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>21341.46</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/13 10:45:12</t>
+          <t>07/13 12:08:35</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>600000</t>
+          <t>175000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>21341.46</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/12 14:43:07</t>
+          <t>07/13 10:45:12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>600000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/10 14:54:56</t>
+          <t>07/12 14:43:07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>36809.82</t>
+          <t>18404.91</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/10 13:44:44</t>
+          <t>07/10 14:54:56</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>36809.82</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/10 13:24:33</t>
+          <t>07/10 13:44:44</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>29543.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/09 20:44:16</t>
+          <t>07/10 13:24:33</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>29543.18</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/09 09:52:57</t>
+          <t>07/09 20:44:16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/09 09:52:18</t>
+          <t>07/09 09:52:57</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>45962.73</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/09 09:51:15</t>
+          <t>07/09 09:52:18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>45962.73</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/08 11:55:35</t>
+          <t>07/09 09:51:15</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>124223.6</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/08 11:27:56</t>
+          <t>07/08 11:55:35</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>23952.1</t>
+          <t>124223.6</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/07 17:03:42</t>
+          <t>07/08 11:27:56</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>23952.1</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,39 +1098,39 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,39 +1140,39 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,22 +1308,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,22 +1350,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,12 +1518,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1713,12 +1713,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1797,12 +1797,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1881,12 +1881,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1965,12 +1965,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2049,12 +2049,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2091,12 +2091,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2106,12 +2106,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2133,12 +2133,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2175,12 +2175,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2217,166 +2217,181 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="57"/>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="58"/>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="60"/>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="61"/>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2398,12 +2413,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2425,83 +2440,110 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="67"/>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="68"/>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>14475347</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1787243.27</t>
+          <t>14659190</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1809800.69</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>1786141.27</t>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1808698.69</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/17 18:14:47</t>
+          <t>07/17 18:38:51</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>183843</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>22557.42</t>
+          <t>46250</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/17 17:10:27</t>
+          <t>07/17 18:14:47</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>183843</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>22557.42</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/17 15:25:18</t>
+          <t>07/17 17:10:27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/17 10:45:36</t>
+          <t>07/17 15:25:18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13671.07</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/16 12:19:58</t>
+          <t>07/17 10:45:36</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>13671.07</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/15 19:20:32</t>
+          <t>07/16 12:19:58</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/15 16:22:26</t>
+          <t>07/15 19:20:32</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>13496.93</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/14 19:36:11</t>
+          <t>07/15 16:22:26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>28395.06</t>
+          <t>13496.93</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/13 13:36:47</t>
+          <t>07/14 19:36:11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>28395.06</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/13 12:08:35</t>
+          <t>07/13 13:36:47</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>21341.46</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/13 10:45:12</t>
+          <t>07/13 12:08:35</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>600000</t>
+          <t>175000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>21341.46</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/12 14:43:07</t>
+          <t>07/13 10:45:12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>600000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/10 14:54:56</t>
+          <t>07/12 14:43:07</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>36809.82</t>
+          <t>18404.91</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/10 13:44:44</t>
+          <t>07/10 14:54:56</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>36809.82</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/10 13:24:33</t>
+          <t>07/10 13:44:44</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>29543.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/09 20:44:16</t>
+          <t>07/10 13:24:33</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>29543.18</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,7 +747,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/09 09:52:57</t>
+          <t>07/09 20:44:16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/09 09:52:18</t>
+          <t>07/09 09:52:57</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>45962.73</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/09 09:51:15</t>
+          <t>07/09 09:52:18</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>45962.73</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/08 11:55:35</t>
+          <t>07/09 09:51:15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>124223.6</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/08 11:27:56</t>
+          <t>07/08 11:55:35</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>23952.1</t>
+          <t>124223.6</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/07 17:03:42</t>
+          <t>07/08 11:27:56</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>23952.1</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,39 +1140,39 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,39 +1182,39 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,22 +1350,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,22 +1392,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,12 +1518,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1713,12 +1713,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1797,12 +1797,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1881,12 +1881,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1965,12 +1965,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2049,12 +2049,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2091,12 +2091,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2133,12 +2133,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2175,12 +2175,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2217,12 +2217,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2259,166 +2259,181 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="58"/>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="59"/>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="61"/>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="62"/>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2440,12 +2455,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2467,83 +2482,110 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="68"/>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="69"/>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>14659190</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1809800.69</t>
+          <t>15029190</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1856050.69</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>1808698.69</t>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1854948.69</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/17 18:38:51</t>
+          <t>07/19 19:17:33</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>46250</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/17 18:14:47</t>
+          <t>07/17 18:38:51</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>183843</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>22557.42</t>
+          <t>46250</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/17 17:10:27</t>
+          <t>07/17 18:14:47</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>183843</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>22557.42</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/17 15:25:18</t>
+          <t>07/17 17:10:27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/17 10:45:36</t>
+          <t>07/17 15:25:18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>13671.07</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/16 12:19:58</t>
+          <t>07/17 10:45:36</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>13671.07</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/15 19:20:32</t>
+          <t>07/16 12:19:58</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/15 16:22:26</t>
+          <t>07/15 19:20:32</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>13496.93</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/14 19:36:11</t>
+          <t>07/15 16:22:26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>28395.06</t>
+          <t>13496.93</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/13 13:36:47</t>
+          <t>07/14 19:36:11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>28395.06</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/13 12:08:35</t>
+          <t>07/13 13:36:47</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>21341.46</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/13 10:45:12</t>
+          <t>07/13 12:08:35</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>600000</t>
+          <t>175000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>21341.46</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/12 14:43:07</t>
+          <t>07/13 10:45:12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>600000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/10 14:54:56</t>
+          <t>07/12 14:43:07</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>36809.82</t>
+          <t>18404.91</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/10 13:44:44</t>
+          <t>07/10 14:54:56</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>36809.82</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/10 13:24:33</t>
+          <t>07/10 13:44:44</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>29543.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/09 20:44:16</t>
+          <t>07/10 13:24:33</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>29543.18</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,7 +789,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/09 09:52:57</t>
+          <t>07/09 20:44:16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/09 09:52:18</t>
+          <t>07/09 09:52:57</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>45962.73</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/09 09:51:15</t>
+          <t>07/09 09:52:18</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>45962.73</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/08 11:55:35</t>
+          <t>07/09 09:51:15</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>124223.6</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/08 11:27:56</t>
+          <t>07/08 11:55:35</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>23952.1</t>
+          <t>124223.6</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/07 17:03:42</t>
+          <t>07/08 11:27:56</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>23952.1</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,39 +1182,39 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,39 +1224,39 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,22 +1392,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,22 +1434,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,12 +1518,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1713,12 +1713,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1797,12 +1797,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1881,12 +1881,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1965,12 +1965,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2049,12 +2049,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2091,12 +2091,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2133,12 +2133,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2175,12 +2175,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2217,12 +2217,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2259,12 +2259,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2274,12 +2274,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2301,166 +2301,181 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="59"/>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="60"/>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="62"/>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="63"/>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2482,12 +2497,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2509,83 +2524,110 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="69"/>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="70"/>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>15029190</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1856050.69</t>
+          <t>15129190</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1868320.63</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>1854948.69</t>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1867218.63</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/19 19:17:33</t>
+          <t>07/20 13:58:56</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>7361.96</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/17 18:38:51</t>
+          <t>07/19 19:17:33</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>46250</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/17 18:14:47</t>
+          <t>07/17 18:38:51</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>183843</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>22557.42</t>
+          <t>46250</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/17 17:10:27</t>
+          <t>07/17 18:14:47</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>183843</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>22557.42</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/17 15:25:18</t>
+          <t>07/17 17:10:27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/17 10:45:36</t>
+          <t>07/17 15:25:18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>13671.07</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/16 12:19:58</t>
+          <t>07/17 10:45:36</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>13671.07</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/15 19:20:32</t>
+          <t>07/16 12:19:58</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/15 16:22:26</t>
+          <t>07/15 19:20:32</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13496.93</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/14 19:36:11</t>
+          <t>07/15 16:22:26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>28395.06</t>
+          <t>13496.93</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/13 13:36:47</t>
+          <t>07/14 19:36:11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>28395.06</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/13 12:08:35</t>
+          <t>07/13 13:36:47</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>21341.46</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/13 10:45:12</t>
+          <t>07/13 12:08:35</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>600000</t>
+          <t>175000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>21341.46</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/12 14:43:07</t>
+          <t>07/13 10:45:12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>600000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/10 14:54:56</t>
+          <t>07/12 14:43:07</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>36809.82</t>
+          <t>18404.91</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/10 13:44:44</t>
+          <t>07/10 14:54:56</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>36809.82</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/10 13:24:33</t>
+          <t>07/10 13:44:44</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>29543.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/09 20:44:16</t>
+          <t>07/10 13:24:33</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>29543.18</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/09 09:52:57</t>
+          <t>07/09 20:44:16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/09 09:52:18</t>
+          <t>07/09 09:52:57</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>45962.73</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/09 09:51:15</t>
+          <t>07/09 09:52:18</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>45962.73</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/08 11:55:35</t>
+          <t>07/09 09:51:15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>124223.6</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/08 11:27:56</t>
+          <t>07/08 11:55:35</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>23952.1</t>
+          <t>124223.6</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/07 17:03:42</t>
+          <t>07/08 11:27:56</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>23952.1</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,39 +1224,39 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,39 +1266,39 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,22 +1434,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,22 +1476,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,12 +1518,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1713,12 +1713,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1797,12 +1797,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1881,12 +1881,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1965,12 +1965,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2049,12 +2049,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2091,12 +2091,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2133,12 +2133,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2175,12 +2175,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2217,12 +2217,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2259,12 +2259,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2274,12 +2274,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2301,12 +2301,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2316,12 +2316,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2343,166 +2343,181 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="60"/>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="61"/>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="63"/>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2524,12 +2539,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2551,83 +2566,110 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="70"/>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="71"/>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>15129190</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1868320.63</t>
+          <t>15189190</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1875682.59</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>1867218.63</t>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>1874580.59</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -2512,12 +2512,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>07/20 14:01:29</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>438</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2539,12 +2539,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2566,12 +2566,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2593,83 +2593,110 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="71"/>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="72"/>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>15189190</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1875682.59</t>
+          <t>15189190</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1875682.59</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>1874580.59</t>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1874142.59</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/20 13:58:56</t>
+          <t>07/21 14:22:59</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>7361.96</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/19 19:17:33</t>
+          <t>07/20 13:58:56</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>7361.96</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/17 18:38:51</t>
+          <t>07/19 19:17:33</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>46250</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/17 18:14:47</t>
+          <t>07/17 18:38:51</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>183843</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>22557.42</t>
+          <t>46250</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/17 17:10:27</t>
+          <t>07/17 18:14:47</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>183843</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>22557.42</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/17 15:25:18</t>
+          <t>07/17 17:10:27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/17 10:45:36</t>
+          <t>07/17 15:25:18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>13671.07</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/16 12:19:58</t>
+          <t>07/17 10:45:36</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>13671.07</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/15 19:20:32</t>
+          <t>07/16 12:19:58</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/15 16:22:26</t>
+          <t>07/15 19:20:32</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>13496.93</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/14 19:36:11</t>
+          <t>07/15 16:22:26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>28395.06</t>
+          <t>13496.93</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/13 13:36:47</t>
+          <t>07/14 19:36:11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>28395.06</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/13 12:08:35</t>
+          <t>07/13 13:36:47</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>21341.46</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/13 10:45:12</t>
+          <t>07/13 12:08:35</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>600000</t>
+          <t>175000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>21341.46</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/12 14:43:07</t>
+          <t>07/13 10:45:12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>600000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/10 14:54:56</t>
+          <t>07/12 14:43:07</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>36809.82</t>
+          <t>18404.91</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/10 13:44:44</t>
+          <t>07/10 14:54:56</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>36809.82</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/10 13:24:33</t>
+          <t>07/10 13:44:44</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>29543.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/09 20:44:16</t>
+          <t>07/10 13:24:33</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>29543.18</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,7 +873,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/09 09:52:57</t>
+          <t>07/09 20:44:16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/09 09:52:18</t>
+          <t>07/09 09:52:57</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>45962.73</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/09 09:51:15</t>
+          <t>07/09 09:52:18</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>45962.73</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/08 11:55:35</t>
+          <t>07/09 09:51:15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>124223.6</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/08 11:27:56</t>
+          <t>07/08 11:55:35</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>23952.1</t>
+          <t>124223.6</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/07 17:03:42</t>
+          <t>07/08 11:27:56</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>23952.1</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,39 +1266,39 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,39 +1308,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,22 +1476,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,22 +1518,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1713,12 +1713,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1797,12 +1797,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1881,12 +1881,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1965,12 +1965,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2049,12 +2049,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2091,12 +2091,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2133,12 +2133,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2175,12 +2175,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2217,12 +2217,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2259,12 +2259,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2274,12 +2274,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2301,12 +2301,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2316,12 +2316,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2343,12 +2343,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2385,166 +2385,181 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="61"/>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="62"/>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="64"/>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="65"/>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07/20 14:01:29</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>07/20 14:01:29</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>438</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2566,12 +2581,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2593,12 +2608,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2620,83 +2635,110 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="72"/>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="73"/>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>15189190</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1875682.59</t>
+          <t>15289190</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>1887952.53</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>1874142.59</t>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1886412.53</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/21 14:22:59</t>
+          <t>07/22 10:20:48</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>25157.23</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/20 13:58:56</t>
+          <t>07/21 14:22:59</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>7361.96</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/19 19:17:33</t>
+          <t>07/20 13:58:56</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>7361.96</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/17 18:38:51</t>
+          <t>07/19 19:17:33</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>46250</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/17 18:14:47</t>
+          <t>07/17 18:38:51</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>183843</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>22557.42</t>
+          <t>46250</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/17 17:10:27</t>
+          <t>07/17 18:14:47</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>183843</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>22557.42</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/17 15:25:18</t>
+          <t>07/17 17:10:27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/17 10:45:36</t>
+          <t>07/17 15:25:18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>13671.07</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/16 12:19:58</t>
+          <t>07/17 10:45:36</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>13671.07</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/15 19:20:32</t>
+          <t>07/16 12:19:58</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/15 16:22:26</t>
+          <t>07/15 19:20:32</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>13496.93</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/14 19:36:11</t>
+          <t>07/15 16:22:26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>28395.06</t>
+          <t>13496.93</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/13 13:36:47</t>
+          <t>07/14 19:36:11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>28395.06</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/13 12:08:35</t>
+          <t>07/13 13:36:47</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>21341.46</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/13 10:45:12</t>
+          <t>07/13 12:08:35</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>600000</t>
+          <t>175000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>21341.46</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/12 14:43:07</t>
+          <t>07/13 10:45:12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>600000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/10 14:54:56</t>
+          <t>07/12 14:43:07</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>36809.82</t>
+          <t>18404.91</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/10 13:44:44</t>
+          <t>07/10 14:54:56</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>36809.82</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/10 13:24:33</t>
+          <t>07/10 13:44:44</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>29543.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/09 20:44:16</t>
+          <t>07/10 13:24:33</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>29543.18</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,7 +915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/09 09:52:57</t>
+          <t>07/09 20:44:16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/09 09:52:18</t>
+          <t>07/09 09:52:57</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>45962.73</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/09 09:51:15</t>
+          <t>07/09 09:52:18</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>45962.73</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/08 11:55:35</t>
+          <t>07/09 09:51:15</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>124223.6</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/08 11:27:56</t>
+          <t>07/08 11:55:35</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>23952.1</t>
+          <t>124223.6</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/07 17:03:42</t>
+          <t>07/08 11:27:56</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>23952.1</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,39 +1308,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,39 +1350,39 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,22 +1518,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1560,22 +1560,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1713,12 +1713,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1797,12 +1797,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1881,12 +1881,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1965,12 +1965,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2049,12 +2049,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2091,12 +2091,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2106,12 +2106,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2133,12 +2133,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2175,12 +2175,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2217,12 +2217,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2259,12 +2259,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2301,12 +2301,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2316,12 +2316,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2343,12 +2343,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2385,12 +2385,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2427,166 +2427,181 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="62"/>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="63"/>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="65"/>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="66"/>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07/20 14:01:29</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>07/20 14:01:29</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>438</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2608,12 +2623,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2635,12 +2650,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2662,83 +2677,110 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="73"/>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="74"/>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>15289190</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1887952.53</t>
+          <t>15489190</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>1913109.76</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>1886412.53</t>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1911569.76</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/22 10:20:48</t>
+          <t>07/22 14:46:31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>274950</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>25157.23</t>
+          <t>33530.49</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/21 14:22:59</t>
+          <t>07/22 10:20:48</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>25157.23</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/20 13:58:56</t>
+          <t>07/21 14:22:59</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>7361.96</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/19 19:17:33</t>
+          <t>07/20 13:58:56</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>7361.96</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/17 18:38:51</t>
+          <t>07/19 19:17:33</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>46250</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/17 18:14:47</t>
+          <t>07/17 18:38:51</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>183843</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>22557.42</t>
+          <t>46250</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/17 17:10:27</t>
+          <t>07/17 18:14:47</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>183843</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>22557.42</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/17 15:25:18</t>
+          <t>07/17 17:10:27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/17 10:45:36</t>
+          <t>07/17 15:25:18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13671.07</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/16 12:19:58</t>
+          <t>07/17 10:45:36</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>13671.07</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/15 19:20:32</t>
+          <t>07/16 12:19:58</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/15 16:22:26</t>
+          <t>07/15 19:20:32</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>13496.93</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/14 19:36:11</t>
+          <t>07/15 16:22:26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>28395.06</t>
+          <t>13496.93</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/13 13:36:47</t>
+          <t>07/14 19:36:11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>28395.06</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/13 12:08:35</t>
+          <t>07/13 13:36:47</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>21341.46</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/13 10:45:12</t>
+          <t>07/13 12:08:35</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>600000</t>
+          <t>175000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>21341.46</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/12 14:43:07</t>
+          <t>07/13 10:45:12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>600000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/10 14:54:56</t>
+          <t>07/12 14:43:07</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>36809.82</t>
+          <t>18404.91</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/10 13:44:44</t>
+          <t>07/10 14:54:56</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>36809.82</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/10 13:24:33</t>
+          <t>07/10 13:44:44</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>29543.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/09 20:44:16</t>
+          <t>07/10 13:24:33</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>29543.18</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,7 +957,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/09 09:52:57</t>
+          <t>07/09 20:44:16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/09 09:52:18</t>
+          <t>07/09 09:52:57</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>45962.73</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/09 09:51:15</t>
+          <t>07/09 09:52:18</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>45962.73</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/08 11:55:35</t>
+          <t>07/09 09:51:15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>124223.6</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/08 11:27:56</t>
+          <t>07/08 11:55:35</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>23952.1</t>
+          <t>124223.6</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/07 17:03:42</t>
+          <t>07/08 11:27:56</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>23952.1</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,39 +1350,39 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,39 +1392,39 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,12 +1518,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1560,22 +1560,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1602,22 +1602,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1713,12 +1713,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1797,12 +1797,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1881,12 +1881,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1965,12 +1965,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2049,12 +2049,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2091,12 +2091,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2133,12 +2133,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2175,12 +2175,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2217,12 +2217,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2259,12 +2259,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2301,12 +2301,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2343,12 +2343,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2385,12 +2385,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2427,12 +2427,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2469,166 +2469,181 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="63"/>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="66"/>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="67"/>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07/20 14:01:29</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>07/20 14:01:29</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>438</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2650,12 +2665,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2677,12 +2692,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2704,83 +2719,110 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="74"/>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="75"/>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>15489190</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1913109.76</t>
+          <t>15764140</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>1946640.25</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>1911569.76</t>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1945100.25</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/22 14:46:31</t>
+          <t>07/22 14:50:27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>274950</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>33530.49</t>
+          <t>9638.55</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/22 10:20:48</t>
+          <t>07/22 14:46:31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>274950</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>25157.23</t>
+          <t>33530.49</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/21 14:22:59</t>
+          <t>07/22 10:20:48</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>25157.23</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/20 13:58:56</t>
+          <t>07/21 14:22:59</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7361.96</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/19 19:17:33</t>
+          <t>07/20 13:58:56</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>7361.96</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/17 18:38:51</t>
+          <t>07/19 19:17:33</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>46250</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/17 18:14:47</t>
+          <t>07/17 18:38:51</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>183843</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>22557.42</t>
+          <t>46250</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/17 17:10:27</t>
+          <t>07/17 18:14:47</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>183843</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>22557.42</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/17 15:25:18</t>
+          <t>07/17 17:10:27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/17 10:45:36</t>
+          <t>07/17 15:25:18</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>13671.07</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/16 12:19:58</t>
+          <t>07/17 10:45:36</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>13671.07</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/15 19:20:32</t>
+          <t>07/16 12:19:58</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/15 16:22:26</t>
+          <t>07/15 19:20:32</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13496.93</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/14 19:36:11</t>
+          <t>07/15 16:22:26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>28395.06</t>
+          <t>13496.93</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/13 13:36:47</t>
+          <t>07/14 19:36:11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>28395.06</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/13 12:08:35</t>
+          <t>07/13 13:36:47</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>21341.46</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/13 10:45:12</t>
+          <t>07/13 12:08:35</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>600000</t>
+          <t>175000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>21341.46</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/12 14:43:07</t>
+          <t>07/13 10:45:12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>600000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/10 14:54:56</t>
+          <t>07/12 14:43:07</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>36809.82</t>
+          <t>18404.91</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/10 13:44:44</t>
+          <t>07/10 14:54:56</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>36809.82</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/10 13:24:33</t>
+          <t>07/10 13:44:44</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>29543.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/09 20:44:16</t>
+          <t>07/10 13:24:33</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>29543.18</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,7 +999,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/09 09:52:57</t>
+          <t>07/09 20:44:16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/09 09:52:18</t>
+          <t>07/09 09:52:57</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>45962.73</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/09 09:51:15</t>
+          <t>07/09 09:52:18</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>45962.73</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/08 11:55:35</t>
+          <t>07/09 09:51:15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>124223.6</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/08 11:27:56</t>
+          <t>07/08 11:55:35</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>23952.1</t>
+          <t>124223.6</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/07 17:03:42</t>
+          <t>07/08 11:27:56</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>23952.1</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,39 +1392,39 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,39 +1434,39 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,12 +1518,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1602,22 +1602,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1644,22 +1644,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1713,12 +1713,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1797,12 +1797,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1881,12 +1881,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1965,12 +1965,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2049,12 +2049,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2091,12 +2091,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2133,12 +2133,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2175,12 +2175,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2217,12 +2217,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2259,12 +2259,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2301,12 +2301,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2343,12 +2343,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2385,12 +2385,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2427,12 +2427,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2469,12 +2469,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2511,166 +2511,181 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="64"/>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="65"/>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="67"/>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="68"/>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07/20 14:01:29</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>07/20 14:01:29</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>438</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2692,12 +2707,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2719,12 +2734,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2746,83 +2761,110 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="75"/>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="76"/>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>15764140</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1946640.25</t>
+          <t>15844140</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>1956278.8</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>1945100.25</t>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1954738.8</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/22 14:50:27</t>
+          <t>07/23 09:57:25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>420000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9638.55</t>
+          <t>52500</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/22 14:46:31</t>
+          <t>07/22 14:50:27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>274950</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>33530.49</t>
+          <t>9638.55</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/22 10:20:48</t>
+          <t>07/22 14:46:31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>274950</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>25157.23</t>
+          <t>33530.49</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/21 14:22:59</t>
+          <t>07/22 10:20:48</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>25157.23</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/20 13:58:56</t>
+          <t>07/21 14:22:59</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>7361.96</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/19 19:17:33</t>
+          <t>07/20 13:58:56</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>7361.96</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/17 18:38:51</t>
+          <t>07/19 19:17:33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>46250</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/17 18:14:47</t>
+          <t>07/17 18:38:51</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>183843</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>22557.42</t>
+          <t>46250</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/17 17:10:27</t>
+          <t>07/17 18:14:47</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>183843</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>22557.42</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/17 15:25:18</t>
+          <t>07/17 17:10:27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/17 10:45:36</t>
+          <t>07/17 15:25:18</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>13671.07</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/16 12:19:58</t>
+          <t>07/17 10:45:36</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>13671.07</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/15 19:20:32</t>
+          <t>07/16 12:19:58</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/15 16:22:26</t>
+          <t>07/15 19:20:32</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>13496.93</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/14 19:36:11</t>
+          <t>07/15 16:22:26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>28395.06</t>
+          <t>13496.93</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/13 13:36:47</t>
+          <t>07/14 19:36:11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>28395.06</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/13 12:08:35</t>
+          <t>07/13 13:36:47</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>21341.46</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/13 10:45:12</t>
+          <t>07/13 12:08:35</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>600000</t>
+          <t>175000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>21341.46</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/12 14:43:07</t>
+          <t>07/13 10:45:12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>600000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/10 14:54:56</t>
+          <t>07/12 14:43:07</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>36809.82</t>
+          <t>18404.91</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/10 13:44:44</t>
+          <t>07/10 14:54:56</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>36809.82</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/10 13:24:33</t>
+          <t>07/10 13:44:44</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>29543.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/09 20:44:16</t>
+          <t>07/10 13:24:33</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>29543.18</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,7 +1041,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/09 09:52:57</t>
+          <t>07/09 20:44:16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/09 09:52:18</t>
+          <t>07/09 09:52:57</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>45962.73</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/09 09:51:15</t>
+          <t>07/09 09:52:18</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>45962.73</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/08 11:55:35</t>
+          <t>07/09 09:51:15</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>124223.6</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/08 11:27:56</t>
+          <t>07/08 11:55:35</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>23952.1</t>
+          <t>124223.6</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/07 17:03:42</t>
+          <t>07/08 11:27:56</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>23952.1</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,39 +1434,39 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,39 +1476,39 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,12 +1518,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1644,22 +1644,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1686,22 +1686,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -1713,12 +1713,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1797,12 +1797,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1881,12 +1881,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1965,12 +1965,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2049,12 +2049,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2091,12 +2091,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2106,12 +2106,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2133,12 +2133,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2175,12 +2175,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2217,12 +2217,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2259,12 +2259,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2301,12 +2301,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2343,12 +2343,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2385,12 +2385,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2427,12 +2427,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2469,12 +2469,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2511,12 +2511,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2526,12 +2526,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2553,166 +2553,181 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="65"/>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="66"/>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="68"/>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="69"/>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07/20 14:01:29</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>07/20 14:01:29</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>438</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2734,12 +2749,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2761,12 +2776,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2788,83 +2803,110 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="76"/>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="77"/>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>15844140</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1956278.8</t>
+          <t>16264140</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>2008778.8</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>1954738.8</t>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2007238.8</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/23 09:57:25</t>
+          <t>07/23 10:04:03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>420000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>52500</t>
+          <t>50314.47</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/22 14:50:27</t>
+          <t>07/23 09:57:25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>420000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>9638.55</t>
+          <t>52500</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/22 14:46:31</t>
+          <t>07/22 14:50:27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>274950</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>33530.49</t>
+          <t>9638.55</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/22 10:20:48</t>
+          <t>07/22 14:46:31</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>274950</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>25157.23</t>
+          <t>33530.49</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/21 14:22:59</t>
+          <t>07/22 10:20:48</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>25157.23</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/20 13:58:56</t>
+          <t>07/21 14:22:59</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7361.96</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/19 19:17:33</t>
+          <t>07/20 13:58:56</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>7361.96</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/17 18:38:51</t>
+          <t>07/19 19:17:33</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>46250</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/17 18:14:47</t>
+          <t>07/17 18:38:51</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>183843</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>22557.42</t>
+          <t>46250</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/17 17:10:27</t>
+          <t>07/17 18:14:47</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>183843</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>22557.42</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/17 15:25:18</t>
+          <t>07/17 17:10:27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/17 10:45:36</t>
+          <t>07/17 15:25:18</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>13671.07</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/16 12:19:58</t>
+          <t>07/17 10:45:36</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>13671.07</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/15 19:20:32</t>
+          <t>07/16 12:19:58</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/15 16:22:26</t>
+          <t>07/15 19:20:32</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13496.93</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/14 19:36:11</t>
+          <t>07/15 16:22:26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>28395.06</t>
+          <t>13496.93</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/13 13:36:47</t>
+          <t>07/14 19:36:11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>28395.06</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/13 12:08:35</t>
+          <t>07/13 13:36:47</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>21341.46</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/13 10:45:12</t>
+          <t>07/13 12:08:35</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>600000</t>
+          <t>175000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>21341.46</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/12 14:43:07</t>
+          <t>07/13 10:45:12</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>600000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/10 14:54:56</t>
+          <t>07/12 14:43:07</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>36809.82</t>
+          <t>18404.91</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/10 13:44:44</t>
+          <t>07/10 14:54:56</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>36809.82</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/10 13:24:33</t>
+          <t>07/10 13:44:44</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>29543.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/09 20:44:16</t>
+          <t>07/10 13:24:33</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>29543.18</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,7 +1083,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/09 09:52:57</t>
+          <t>07/09 20:44:16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/09 09:52:18</t>
+          <t>07/09 09:52:57</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>45962.73</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/09 09:51:15</t>
+          <t>07/09 09:52:18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>45962.73</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/08 11:55:35</t>
+          <t>07/09 09:51:15</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>124223.6</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/08 11:27:56</t>
+          <t>07/08 11:55:35</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>23952.1</t>
+          <t>124223.6</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/07 17:03:42</t>
+          <t>07/08 11:27:56</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>23952.1</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,39 +1476,39 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,39 +1518,39 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1686,22 +1686,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -1713,12 +1713,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1728,22 +1728,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1797,12 +1797,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1881,12 +1881,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1965,12 +1965,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2049,12 +2049,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2091,12 +2091,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2106,12 +2106,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2133,12 +2133,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2175,12 +2175,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2217,12 +2217,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2259,12 +2259,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2274,12 +2274,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2301,12 +2301,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2343,12 +2343,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2385,12 +2385,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2427,12 +2427,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2469,12 +2469,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2511,12 +2511,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2526,12 +2526,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2553,12 +2553,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2595,166 +2595,181 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="66"/>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="67"/>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="69"/>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="70"/>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07/20 14:01:29</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>07/20 14:01:29</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>438</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2776,12 +2791,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2803,12 +2818,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2830,83 +2845,110 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="77"/>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="78"/>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>16264140</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2008778.8</t>
+          <t>16664140</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>2059093.27</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>2007238.8</t>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2057553.27</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/23 10:04:03</t>
+          <t>07/23 10:46:36</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>50314.47</t>
+          <t>30864.2</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/23 09:57:25</t>
+          <t>07/23 10:04:03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>420000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>52500</t>
+          <t>50314.47</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/22 14:50:27</t>
+          <t>07/23 09:57:25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>420000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>9638.55</t>
+          <t>52500</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/22 14:46:31</t>
+          <t>07/22 14:50:27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>274950</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>33530.49</t>
+          <t>9638.55</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/22 10:20:48</t>
+          <t>07/22 14:46:31</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>274950</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>25157.23</t>
+          <t>33530.49</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/21 14:22:59</t>
+          <t>07/22 10:20:48</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>25157.23</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/20 13:58:56</t>
+          <t>07/21 14:22:59</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7361.96</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/19 19:17:33</t>
+          <t>07/20 13:58:56</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>7361.96</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/17 18:38:51</t>
+          <t>07/19 19:17:33</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>46250</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/17 18:14:47</t>
+          <t>07/17 18:38:51</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>183843</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>22557.42</t>
+          <t>46250</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/17 17:10:27</t>
+          <t>07/17 18:14:47</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>183843</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>22557.42</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/17 15:25:18</t>
+          <t>07/17 17:10:27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/17 10:45:36</t>
+          <t>07/17 15:25:18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13671.07</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/16 12:19:58</t>
+          <t>07/17 10:45:36</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>13671.07</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/15 19:20:32</t>
+          <t>07/16 12:19:58</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/15 16:22:26</t>
+          <t>07/15 19:20:32</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>13496.93</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/14 19:36:11</t>
+          <t>07/15 16:22:26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>28395.06</t>
+          <t>13496.93</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/13 13:36:47</t>
+          <t>07/14 19:36:11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>28395.06</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/13 12:08:35</t>
+          <t>07/13 13:36:47</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>21341.46</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/13 10:45:12</t>
+          <t>07/13 12:08:35</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>600000</t>
+          <t>175000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>21341.46</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/12 14:43:07</t>
+          <t>07/13 10:45:12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>600000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/10 14:54:56</t>
+          <t>07/12 14:43:07</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>36809.82</t>
+          <t>18404.91</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/10 13:44:44</t>
+          <t>07/10 14:54:56</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>36809.82</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/10 13:24:33</t>
+          <t>07/10 13:44:44</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>29543.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/09 20:44:16</t>
+          <t>07/10 13:24:33</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>29543.18</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,7 +1125,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/09 09:52:57</t>
+          <t>07/09 20:44:16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/09 09:52:18</t>
+          <t>07/09 09:52:57</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>45962.73</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/09 09:51:15</t>
+          <t>07/09 09:52:18</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>45962.73</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/08 11:55:35</t>
+          <t>07/09 09:51:15</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>124223.6</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/08 11:27:56</t>
+          <t>07/08 11:55:35</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>23952.1</t>
+          <t>124223.6</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/07 17:03:42</t>
+          <t>07/08 11:27:56</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>23952.1</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,39 +1518,39 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1560,39 +1560,39 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1713,12 +1713,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1728,22 +1728,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1770,22 +1770,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -1797,12 +1797,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1881,12 +1881,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1965,12 +1965,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2049,12 +2049,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2091,12 +2091,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2106,12 +2106,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2133,12 +2133,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2175,12 +2175,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2217,12 +2217,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2259,12 +2259,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2301,12 +2301,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2316,12 +2316,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2343,12 +2343,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2385,12 +2385,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2427,12 +2427,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2469,12 +2469,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2511,12 +2511,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2526,12 +2526,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2553,12 +2553,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2595,12 +2595,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2637,166 +2637,181 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="67"/>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="68"/>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="70"/>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="71"/>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07/20 14:01:29</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>07/20 14:01:29</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>438</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2818,12 +2833,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2845,12 +2860,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2872,83 +2887,110 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="78"/>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="79"/>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>16664140</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2059093.27</t>
+          <t>16914140</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>2089957.47</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>2057553.27</t>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2088417.47</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/23 10:46:36</t>
+          <t>07/24 10:09:54</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30864.2</t>
+          <t>15662.65</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/23 10:04:03</t>
+          <t>07/23 10:46:36</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>50314.47</t>
+          <t>30864.2</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/23 09:57:25</t>
+          <t>07/23 10:04:03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>420000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>52500</t>
+          <t>50314.47</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/22 14:50:27</t>
+          <t>07/23 09:57:25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>420000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>9638.55</t>
+          <t>52500</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/22 14:46:31</t>
+          <t>07/22 14:50:27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>274950</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>33530.49</t>
+          <t>9638.55</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/22 10:20:48</t>
+          <t>07/22 14:46:31</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>274950</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>25157.23</t>
+          <t>33530.49</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/21 14:22:59</t>
+          <t>07/22 10:20:48</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>25157.23</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/20 13:58:56</t>
+          <t>07/21 14:22:59</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>7361.96</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/19 19:17:33</t>
+          <t>07/20 13:58:56</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>7361.96</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/17 18:38:51</t>
+          <t>07/19 19:17:33</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>46250</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/17 18:14:47</t>
+          <t>07/17 18:38:51</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>183843</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>22557.42</t>
+          <t>46250</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/17 17:10:27</t>
+          <t>07/17 18:14:47</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>183843</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>22557.42</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/17 15:25:18</t>
+          <t>07/17 17:10:27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/17 10:45:36</t>
+          <t>07/17 15:25:18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>13671.07</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/16 12:19:58</t>
+          <t>07/17 10:45:36</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>13671.07</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/15 19:20:32</t>
+          <t>07/16 12:19:58</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/15 16:22:26</t>
+          <t>07/15 19:20:32</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>13496.93</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/14 19:36:11</t>
+          <t>07/15 16:22:26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>28395.06</t>
+          <t>13496.93</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/13 13:36:47</t>
+          <t>07/14 19:36:11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>28395.06</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/13 12:08:35</t>
+          <t>07/13 13:36:47</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>21341.46</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/13 10:45:12</t>
+          <t>07/13 12:08:35</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>600000</t>
+          <t>175000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>21341.46</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/12 14:43:07</t>
+          <t>07/13 10:45:12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>600000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/10 14:54:56</t>
+          <t>07/12 14:43:07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>36809.82</t>
+          <t>18404.91</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/10 13:44:44</t>
+          <t>07/10 14:54:56</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>36809.82</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/10 13:24:33</t>
+          <t>07/10 13:44:44</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>29543.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/09 20:44:16</t>
+          <t>07/10 13:24:33</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>29543.18</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,7 +1167,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/09 09:52:57</t>
+          <t>07/09 20:44:16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/09 09:52:18</t>
+          <t>07/09 09:52:57</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>45962.73</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/09 09:51:15</t>
+          <t>07/09 09:52:18</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>45962.73</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/08 11:55:35</t>
+          <t>07/09 09:51:15</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>124223.6</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/08 11:27:56</t>
+          <t>07/08 11:55:35</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>23952.1</t>
+          <t>124223.6</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/07 17:03:42</t>
+          <t>07/08 11:27:56</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>23952.1</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,12 +1518,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1560,39 +1560,39 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1602,39 +1602,39 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1713,12 +1713,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1770,22 +1770,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -1797,12 +1797,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1812,22 +1812,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1881,12 +1881,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1965,12 +1965,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2049,12 +2049,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2091,12 +2091,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2106,12 +2106,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2133,12 +2133,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2175,12 +2175,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2217,12 +2217,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2259,12 +2259,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2301,12 +2301,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2343,12 +2343,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2385,12 +2385,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2427,12 +2427,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2469,12 +2469,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2511,12 +2511,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2553,12 +2553,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2595,12 +2595,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2637,12 +2637,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2652,12 +2652,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2679,166 +2679,181 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="68"/>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="69"/>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="71"/>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="72"/>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07/20 14:01:29</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>07/20 14:01:29</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>438</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2860,12 +2875,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2887,12 +2902,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2914,83 +2929,110 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="79"/>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="80"/>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>16914140</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2089957.47</t>
+          <t>17044140</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>2105620.12</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>2088417.47</t>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2104080.12</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/24 10:09:54</t>
+          <t>07/24 11:18:18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>15662.65</t>
+          <t>21383.65</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/23 10:46:36</t>
+          <t>07/24 10:09:54</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30864.2</t>
+          <t>15662.65</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/23 10:04:03</t>
+          <t>07/23 10:46:36</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>50314.47</t>
+          <t>30864.2</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/23 09:57:25</t>
+          <t>07/23 10:04:03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>420000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>52500</t>
+          <t>50314.47</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/22 14:50:27</t>
+          <t>07/23 09:57:25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>420000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>9638.55</t>
+          <t>52500</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/22 14:46:31</t>
+          <t>07/22 14:50:27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>274950</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>33530.49</t>
+          <t>9638.55</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/22 10:20:48</t>
+          <t>07/22 14:46:31</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>274950</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>25157.23</t>
+          <t>33530.49</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/21 14:22:59</t>
+          <t>07/22 10:20:48</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>25157.23</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/20 13:58:56</t>
+          <t>07/21 14:22:59</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>7361.96</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/19 19:17:33</t>
+          <t>07/20 13:58:56</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>7361.96</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/17 18:38:51</t>
+          <t>07/19 19:17:33</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>46250</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/17 18:14:47</t>
+          <t>07/17 18:38:51</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>183843</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>22557.42</t>
+          <t>46250</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/17 17:10:27</t>
+          <t>07/17 18:14:47</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>183843</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>22557.42</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/17 15:25:18</t>
+          <t>07/17 17:10:27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/17 10:45:36</t>
+          <t>07/17 15:25:18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13671.07</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/16 12:19:58</t>
+          <t>07/17 10:45:36</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>13671.07</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/15 19:20:32</t>
+          <t>07/16 12:19:58</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/15 16:22:26</t>
+          <t>07/15 19:20:32</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>13496.93</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/14 19:36:11</t>
+          <t>07/15 16:22:26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>28395.06</t>
+          <t>13496.93</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/13 13:36:47</t>
+          <t>07/14 19:36:11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>28395.06</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/13 12:08:35</t>
+          <t>07/13 13:36:47</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>21341.46</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/13 10:45:12</t>
+          <t>07/13 12:08:35</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>600000</t>
+          <t>175000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>21341.46</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/12 14:43:07</t>
+          <t>07/13 10:45:12</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>600000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/10 14:54:56</t>
+          <t>07/12 14:43:07</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>36809.82</t>
+          <t>18404.91</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/10 13:44:44</t>
+          <t>07/10 14:54:56</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>36809.82</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/10 13:24:33</t>
+          <t>07/10 13:44:44</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>29543.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/09 20:44:16</t>
+          <t>07/10 13:24:33</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>29543.18</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,7 +1209,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/09 09:52:57</t>
+          <t>07/09 20:44:16</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/09 09:52:18</t>
+          <t>07/09 09:52:57</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>45962.73</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/09 09:51:15</t>
+          <t>07/09 09:52:18</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>45962.73</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/08 11:55:35</t>
+          <t>07/09 09:51:15</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>124223.6</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/08 11:27:56</t>
+          <t>07/08 11:55:35</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>23952.1</t>
+          <t>124223.6</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/07 17:03:42</t>
+          <t>07/08 11:27:56</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>23952.1</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,12 +1518,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1602,39 +1602,39 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1644,39 +1644,39 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1713,12 +1713,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1797,12 +1797,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1812,22 +1812,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1854,22 +1854,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -1881,12 +1881,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1965,12 +1965,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2049,12 +2049,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2091,12 +2091,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2106,12 +2106,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2133,12 +2133,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2175,12 +2175,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2217,12 +2217,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2259,12 +2259,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2274,12 +2274,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2301,12 +2301,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2343,12 +2343,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2385,12 +2385,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2427,12 +2427,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2469,12 +2469,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2511,12 +2511,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2553,12 +2553,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2595,12 +2595,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2637,12 +2637,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2652,12 +2652,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2679,12 +2679,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2721,166 +2721,181 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="69"/>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="70"/>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="72"/>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="73"/>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07/20 14:01:29</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>07/20 14:01:29</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>438</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2902,12 +2917,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2929,12 +2944,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2956,83 +2971,110 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="80"/>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="81"/>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>17044140</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2105620.12</t>
+          <t>17214140</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>2127003.77</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>2104080.12</t>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2125463.77</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/24 11:18:18</t>
+          <t>07/25 14:40:44</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21383.65</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/24 10:09:54</t>
+          <t>07/24 11:18:18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>15662.65</t>
+          <t>21383.65</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/23 10:46:36</t>
+          <t>07/24 10:09:54</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>30864.2</t>
+          <t>15662.65</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/23 10:04:03</t>
+          <t>07/23 10:46:36</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>50314.47</t>
+          <t>30864.2</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/23 09:57:25</t>
+          <t>07/23 10:04:03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>420000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>52500</t>
+          <t>50314.47</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/22 14:50:27</t>
+          <t>07/23 09:57:25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>420000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>9638.55</t>
+          <t>52500</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/22 14:46:31</t>
+          <t>07/22 14:50:27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>274950</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>33530.49</t>
+          <t>9638.55</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/22 10:20:48</t>
+          <t>07/22 14:46:31</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>274950</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>25157.23</t>
+          <t>33530.49</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/21 14:22:59</t>
+          <t>07/22 10:20:48</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>25157.23</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/20 13:58:56</t>
+          <t>07/21 14:22:59</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>7361.96</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/19 19:17:33</t>
+          <t>07/20 13:58:56</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>7361.96</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/17 18:38:51</t>
+          <t>07/19 19:17:33</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>46250</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/17 18:14:47</t>
+          <t>07/17 18:38:51</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>183843</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>22557.42</t>
+          <t>46250</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/17 17:10:27</t>
+          <t>07/17 18:14:47</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>183843</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>22557.42</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/17 15:25:18</t>
+          <t>07/17 17:10:27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/17 10:45:36</t>
+          <t>07/17 15:25:18</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>13671.07</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/16 12:19:58</t>
+          <t>07/17 10:45:36</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>13671.07</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/15 19:20:32</t>
+          <t>07/16 12:19:58</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/15 16:22:26</t>
+          <t>07/15 19:20:32</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>13496.93</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/14 19:36:11</t>
+          <t>07/15 16:22:26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>28395.06</t>
+          <t>13496.93</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/13 13:36:47</t>
+          <t>07/14 19:36:11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>28395.06</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/13 12:08:35</t>
+          <t>07/13 13:36:47</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>21341.46</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/13 10:45:12</t>
+          <t>07/13 12:08:35</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>600000</t>
+          <t>175000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>21341.46</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/12 14:43:07</t>
+          <t>07/13 10:45:12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>600000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/10 14:54:56</t>
+          <t>07/12 14:43:07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>36809.82</t>
+          <t>18404.91</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/10 13:44:44</t>
+          <t>07/10 14:54:56</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>36809.82</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/10 13:24:33</t>
+          <t>07/10 13:44:44</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>29543.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/09 20:44:16</t>
+          <t>07/10 13:24:33</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>29543.18</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,7 +1251,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/09 09:52:57</t>
+          <t>07/09 20:44:16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/09 09:52:18</t>
+          <t>07/09 09:52:57</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>45962.73</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/09 09:51:15</t>
+          <t>07/09 09:52:18</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>45962.73</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/08 11:55:35</t>
+          <t>07/09 09:51:15</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>124223.6</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/08 11:27:56</t>
+          <t>07/08 11:55:35</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>23952.1</t>
+          <t>124223.6</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/07 17:03:42</t>
+          <t>07/08 11:27:56</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>23952.1</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,12 +1518,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1644,39 +1644,39 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1686,39 +1686,39 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1797,12 +1797,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1854,22 +1854,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -1881,12 +1881,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1896,22 +1896,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1965,12 +1965,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2049,12 +2049,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2091,12 +2091,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2106,12 +2106,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2133,12 +2133,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2175,12 +2175,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2217,12 +2217,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2259,12 +2259,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2274,12 +2274,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2301,12 +2301,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2316,12 +2316,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2343,12 +2343,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2385,12 +2385,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2427,12 +2427,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2469,12 +2469,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2511,12 +2511,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2553,12 +2553,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2595,12 +2595,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2637,12 +2637,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2652,12 +2652,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2679,12 +2679,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2721,12 +2721,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2763,166 +2763,181 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="70"/>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="71"/>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="73"/>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="74"/>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07/20 14:01:29</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>07/20 14:01:29</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>438</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2944,12 +2959,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2971,12 +2986,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2998,83 +3013,110 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="81"/>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="82"/>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>17214140</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2127003.77</t>
+          <t>17314140</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>2139349.44</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>2125463.77</t>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2137809.44</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/25 14:40:44</t>
+          <t>07/26 12:04:38</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/24 11:18:18</t>
+          <t>07/25 14:40:44</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21383.65</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/24 10:09:54</t>
+          <t>07/24 11:18:18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15662.65</t>
+          <t>21383.65</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/23 10:46:36</t>
+          <t>07/24 10:09:54</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>30864.2</t>
+          <t>15662.65</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/23 10:04:03</t>
+          <t>07/23 10:46:36</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>50314.47</t>
+          <t>30864.2</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/23 09:57:25</t>
+          <t>07/23 10:04:03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>420000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>52500</t>
+          <t>50314.47</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/22 14:50:27</t>
+          <t>07/23 09:57:25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>420000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>9638.55</t>
+          <t>52500</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/22 14:46:31</t>
+          <t>07/22 14:50:27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>274950</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>33530.49</t>
+          <t>9638.55</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/22 10:20:48</t>
+          <t>07/22 14:46:31</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>274950</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>25157.23</t>
+          <t>33530.49</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/21 14:22:59</t>
+          <t>07/22 10:20:48</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>25157.23</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/20 13:58:56</t>
+          <t>07/21 14:22:59</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>7361.96</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/19 19:17:33</t>
+          <t>07/20 13:58:56</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>7361.96</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/17 18:38:51</t>
+          <t>07/19 19:17:33</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>46250</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/17 18:14:47</t>
+          <t>07/17 18:38:51</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>183843</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>22557.42</t>
+          <t>46250</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/17 17:10:27</t>
+          <t>07/17 18:14:47</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>183843</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>22557.42</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/17 15:25:18</t>
+          <t>07/17 17:10:27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/17 10:45:36</t>
+          <t>07/17 15:25:18</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>13671.07</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/16 12:19:58</t>
+          <t>07/17 10:45:36</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>13671.07</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/15 19:20:32</t>
+          <t>07/16 12:19:58</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/15 16:22:26</t>
+          <t>07/15 19:20:32</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>13496.93</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/14 19:36:11</t>
+          <t>07/15 16:22:26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>28395.06</t>
+          <t>13496.93</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/13 13:36:47</t>
+          <t>07/14 19:36:11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>28395.06</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/13 12:08:35</t>
+          <t>07/13 13:36:47</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>21341.46</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/13 10:45:12</t>
+          <t>07/13 12:08:35</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>600000</t>
+          <t>175000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>21341.46</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/12 14:43:07</t>
+          <t>07/13 10:45:12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>600000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/10 14:54:56</t>
+          <t>07/12 14:43:07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>36809.82</t>
+          <t>18404.91</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/10 13:44:44</t>
+          <t>07/10 14:54:56</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>36809.82</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/10 13:24:33</t>
+          <t>07/10 13:44:44</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>29543.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/09 20:44:16</t>
+          <t>07/10 13:24:33</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>29543.18</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,7 +1293,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/09 09:52:57</t>
+          <t>07/09 20:44:16</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/09 09:52:18</t>
+          <t>07/09 09:52:57</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>45962.73</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/09 09:51:15</t>
+          <t>07/09 09:52:18</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>45962.73</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/08 11:55:35</t>
+          <t>07/09 09:51:15</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>124223.6</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/08 11:27:56</t>
+          <t>07/08 11:55:35</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>23952.1</t>
+          <t>124223.6</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/07 17:03:42</t>
+          <t>07/08 11:27:56</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,12 +1518,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>23952.1</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1686,39 +1686,39 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1728,39 +1728,39 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1797,12 +1797,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1881,12 +1881,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1896,22 +1896,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1938,22 +1938,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -1965,12 +1965,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2049,12 +2049,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2091,12 +2091,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2106,12 +2106,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2133,12 +2133,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2175,12 +2175,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2217,12 +2217,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2259,12 +2259,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2274,12 +2274,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2301,12 +2301,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2316,12 +2316,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2343,12 +2343,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2385,12 +2385,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2427,12 +2427,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2469,12 +2469,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2511,12 +2511,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2553,12 +2553,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2595,12 +2595,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2637,12 +2637,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2679,12 +2679,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2721,12 +2721,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2763,12 +2763,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2805,166 +2805,181 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="71"/>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="72"/>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="74"/>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="75"/>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07/20 14:01:29</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>07/20 14:01:29</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>438</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2986,12 +3001,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3013,12 +3028,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3040,83 +3055,110 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="82"/>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="83"/>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>17314140</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2139349.44</t>
+          <t>17414140</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>2151544.57</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>2137809.44</t>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2150004.57</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -2974,12 +2974,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07/20 14:01:29</t>
+          <t>07/26 12:04:42</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3001,12 +3001,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>07/20 14:01:29</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>438</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3028,12 +3028,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3055,12 +3055,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3082,83 +3082,110 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="83"/>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="84"/>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>17414140</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2151544.57</t>
+          <t>17414140</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>2151544.57</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>1928</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>2150004.57</t>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2149616.57</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/26 12:04:38</t>
+          <t>07/27 10:20:29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>290000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>36024.84</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>yxhgq79</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,7 +117,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/25 14:40:44</t>
+          <t>07/26 12:04:38</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/24 11:18:18</t>
+          <t>07/25 14:40:44</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>21383.65</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/24 10:09:54</t>
+          <t>07/24 11:18:18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>15662.65</t>
+          <t>21383.65</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/23 10:46:36</t>
+          <t>07/24 10:09:54</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>30864.2</t>
+          <t>15662.65</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/23 10:04:03</t>
+          <t>07/23 10:46:36</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>50314.47</t>
+          <t>30864.2</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/23 09:57:25</t>
+          <t>07/23 10:04:03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>420000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>52500</t>
+          <t>50314.47</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/22 14:50:27</t>
+          <t>07/23 09:57:25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>420000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>9638.55</t>
+          <t>52500</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/22 14:46:31</t>
+          <t>07/22 14:50:27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>274950</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>33530.49</t>
+          <t>9638.55</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/22 10:20:48</t>
+          <t>07/22 14:46:31</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>274950</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>25157.23</t>
+          <t>33530.49</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/21 14:22:59</t>
+          <t>07/22 10:20:48</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>25157.23</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/20 13:58:56</t>
+          <t>07/21 14:22:59</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7361.96</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/19 19:17:33</t>
+          <t>07/20 13:58:56</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>7361.96</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/17 18:38:51</t>
+          <t>07/19 19:17:33</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>46250</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/17 18:14:47</t>
+          <t>07/17 18:38:51</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>183843</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>22557.42</t>
+          <t>46250</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/17 17:10:27</t>
+          <t>07/17 18:14:47</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>183843</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>22557.42</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/17 15:25:18</t>
+          <t>07/17 17:10:27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/17 10:45:36</t>
+          <t>07/17 15:25:18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>13671.07</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/16 12:19:58</t>
+          <t>07/17 10:45:36</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>13671.07</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/15 19:20:32</t>
+          <t>07/16 12:19:58</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/15 16:22:26</t>
+          <t>07/15 19:20:32</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>13496.93</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/14 19:36:11</t>
+          <t>07/15 16:22:26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>28395.06</t>
+          <t>13496.93</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/13 13:36:47</t>
+          <t>07/14 19:36:11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>28395.06</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/13 12:08:35</t>
+          <t>07/13 13:36:47</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>21341.46</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/13 10:45:12</t>
+          <t>07/13 12:08:35</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>600000</t>
+          <t>175000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>21341.46</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/12 14:43:07</t>
+          <t>07/13 10:45:12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>600000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/10 14:54:56</t>
+          <t>07/12 14:43:07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>36809.82</t>
+          <t>18404.91</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/10 13:44:44</t>
+          <t>07/10 14:54:56</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>36809.82</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/10 13:24:33</t>
+          <t>07/10 13:44:44</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>29543.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/09 20:44:16</t>
+          <t>07/10 13:24:33</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>29543.18</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,7 +1335,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/09 09:52:57</t>
+          <t>07/09 20:44:16</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/09 09:52:18</t>
+          <t>07/09 09:52:57</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>45962.73</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/09 09:51:15</t>
+          <t>07/09 09:52:18</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>45962.73</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/08 11:55:35</t>
+          <t>07/09 09:51:15</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>124223.6</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/08 11:27:56</t>
+          <t>07/08 11:55:35</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,12 +1518,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>23952.1</t>
+          <t>124223.6</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/07 17:03:42</t>
+          <t>07/08 11:27:56</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>23952.1</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1713,12 +1713,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1728,39 +1728,39 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1770,39 +1770,39 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1881,12 +1881,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1938,22 +1938,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -1965,12 +1965,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1980,22 +1980,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2049,12 +2049,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2091,12 +2091,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2106,12 +2106,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2133,12 +2133,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2175,12 +2175,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2217,12 +2217,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2259,12 +2259,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2274,12 +2274,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2301,12 +2301,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2316,12 +2316,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2343,12 +2343,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2385,12 +2385,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2427,12 +2427,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2469,12 +2469,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2511,12 +2511,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2526,12 +2526,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2553,12 +2553,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2595,12 +2595,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2637,12 +2637,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2679,12 +2679,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2721,12 +2721,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2763,12 +2763,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2805,12 +2805,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2820,12 +2820,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2847,166 +2847,181 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="72"/>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="73"/>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="75"/>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="76"/>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07/26 12:04:42</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07/20 14:01:29</t>
+          <t>07/26 12:04:42</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3028,12 +3043,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>07/20 14:01:29</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>438</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3055,12 +3070,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3082,12 +3097,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3109,83 +3124,110 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="84"/>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="85"/>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>17414140</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2151544.57</t>
+          <t>17704140</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>2187569.41</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1928</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>2149616.57</t>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2185641.41</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/27 10:20:29</t>
+          <t>07/28 12:19:44</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>290000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>36024.84</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>yxhgq79</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/26 12:04:38</t>
+          <t>07/27 10:20:29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>290000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>36024.84</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>yxhgq79</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,7 +159,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/25 14:40:44</t>
+          <t>07/26 12:04:38</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/24 11:18:18</t>
+          <t>07/25 14:40:44</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>21383.65</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/24 10:09:54</t>
+          <t>07/24 11:18:18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>15662.65</t>
+          <t>21383.65</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/23 10:46:36</t>
+          <t>07/24 10:09:54</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>30864.2</t>
+          <t>15662.65</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/23 10:04:03</t>
+          <t>07/23 10:46:36</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>50314.47</t>
+          <t>30864.2</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/23 09:57:25</t>
+          <t>07/23 10:04:03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>420000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>52500</t>
+          <t>50314.47</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/22 14:50:27</t>
+          <t>07/23 09:57:25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>420000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>9638.55</t>
+          <t>52500</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/22 14:46:31</t>
+          <t>07/22 14:50:27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>274950</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>33530.49</t>
+          <t>9638.55</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/22 10:20:48</t>
+          <t>07/22 14:46:31</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>274950</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>25157.23</t>
+          <t>33530.49</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/21 14:22:59</t>
+          <t>07/22 10:20:48</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>25157.23</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/20 13:58:56</t>
+          <t>07/21 14:22:59</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7361.96</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/19 19:17:33</t>
+          <t>07/20 13:58:56</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>7361.96</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/17 18:38:51</t>
+          <t>07/19 19:17:33</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>46250</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/17 18:14:47</t>
+          <t>07/17 18:38:51</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>183843</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>22557.42</t>
+          <t>46250</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/17 17:10:27</t>
+          <t>07/17 18:14:47</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>183843</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>22557.42</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/17 15:25:18</t>
+          <t>07/17 17:10:27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/17 10:45:36</t>
+          <t>07/17 15:25:18</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>13671.07</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/16 12:19:58</t>
+          <t>07/17 10:45:36</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>13671.07</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/15 19:20:32</t>
+          <t>07/16 12:19:58</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>220000</t>
    